--- a/pacjenci/SYLWESTER JASNOS.xlsx
+++ b/pacjenci/SYLWESTER JASNOS.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Brak aktywnej choroby</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -630,17 +630,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
+          <t>3 - wychwyt nie większy niż wątroba</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
+          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
         </is>
       </c>
     </row>

--- a/pacjenci/SYLWESTER JASNOS.xlsx
+++ b/pacjenci/SYLWESTER JASNOS.xlsx
@@ -413,235 +413,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>04.10.2022</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy. DLBCL - guz jądra lewego. Usunięte jądra lewe (08.2022). Ocena zaawansowania.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 97mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DLBCL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Węzły chłonne w tkance podskórnej w okolicy mięśnia półkolcowego głowy po stronie lewej na poziomie C2 wielkości 12x11,5mm [Im 140].   Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.  Brzuch i miednica: Pobudzenie metaboliczne w topografii wchodów do kanałów pachwinowych oraz pasmowatych zmian bliznowatych w okolicach pachwinowych do przodu od kości łonowych obustronnie na długości do 26mm, SUV max do 4,7 - w pierwszej kolejności procesy gojenia, do  oceny w łączności z całością obrazu klinicznego, ew. do USG. Odcinkowo wzmożony metabolizm FDG w topografii żołądka oraz pętli jelitowych, SUV max do 4,7 - czynnościowo? do ew. kontroli w endoskopii. Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym.  Inne: Pobudzenie metabolicznie w kanale  kręgowym w topografii rdzenia na poziomie Th11 i Th12, SUV max do 3,7.   Wartości referencyjne: MBPS SUVmax 2,5 Prawy płat wątroby SUVmax do 3,5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono pobudzenie metaboliczne w topografii wchodów do kanałów pachwinowych oraz pasmowatych zmian bliznowatych w okolicach pachwinowych do przodu od kości łonowych obustronnie  - w pierwszej kolejności procesy gojenia,  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>4.7</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>13.02.2023</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy. DLBCL - guz jądra lewego. Usunięte jądra lewe (08.2022). Ocena remisji po 2 cyklach RCHOP, 2 cyklach MTX i.v.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 12 min od podania 18F-FDG. Glikemia: 100mg%</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DLBCL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Węzły chłonne w tkance podskórnej w okolicy mięśnia półkolcowego głowy po stronie lewej na poziomie C2 wielkości 12x10mm [Im 140].   Klatka piersiowa i śródpiersie: Pobudzenie metaboliczne we wnęce prawej o wielkości 10x8mm wg PET, SUV max 3,5 [Im 116] - w pierwszej kolejności węzeł chłonny. Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.  Brzuch i miednica: Pobudzenie metaboliczne w topografii wejścia do kanału pachwinowego oraz pasmowatych zmian bliznowatych w okolicy pachwinowej do przodu od kości łonowej po stronie prawej na długości do 13mm, SUV max do 3,7 - w pierwszej kolejności procesy gojenia, do  oceny w łączności z całością obrazu klinicznego, ew. do USG. Odcinkowo wzmożony metabolizm FDG w topografii żołądka oraz pętli jelitowych, SUV max do 5,9 - czynnościowo? do ew. kontroli w endoskopii. Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Dyskopatia C5/6  Inne: Pobudzenie metabolicznie w kanale  kręgowym w topografii rdzenia na poziomie Th11 i Th12, SUV max do 3,7.   Wartości referencyjne: MBPS SUVmax 2,7 Prawy płat wątroby SUVmax do 4,5,</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono pobudzenie metaboliczne we wnęce prawej - w pierwszej kolejności węzeł chłonny - do kontroli. Poza tym uwidoczniono pobudzenie metaboliczne w topografii wejścia do kanału pachwinowego oraz pasmowatych zmian bliznowatych w okolicy pachwinowej do przodu od kości łonowej po stronie prawej (mniejsze niż w badaniu z dnia 04.10.2022) - w pierwszej kolejności procesy gojenia. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>5.9</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>27.06.2023</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy. DLBCL - guz jądra lewego. Usunięte jądro lewe (08.2022). Ocena po zakończeniu immunochemio- i radioterapii.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 56min od podania 18F-FDG. Glikemia: 102mg%</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DLBCL</t>
+          <t>: Miernie pobudzone metabolicznie węzły chłonne przedziału II obustronnie wielkości do 15mm , SUV max do 3,3 - do kontroli.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. W tkance podskórnej w okolicy mięśnia półkolcowego głowy po stronie lewej na poziomie C2 zmiana o niskim cieniowaniu (3HU) wielkości 12x10mm [Im 140] - kaszak ? do oceny miejscowej.   Klatka piersiowa i śródpiersie: Mierne pobudzenie metaboliczne we wnęce prawej  SUV max 3,6 [Im 120] - do ew. kontroli w badaniu TK z kontrastem dożylnym celem wykluczenia obecności węzła chłonnego.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pasmowate zmiany bliznowato-włókniste w płacie środkowym płuca prawego.  Brzuch i miednica: Pobudzenie metaboliczne w topografii wejścia do kanału pachwinowego prawego oraz pasmowatych zmian bliznowatych w okolicy pachwinowej do przodu od kości łonowej po stronie prawej na długości do 16mm, SUV max do 3,8 - w porównaniu do badania z 02.2023 obraz bez istotnych zmian. Odcinkowo wzmożony metabolizm FDG w topografii żołądka, dwunastnicy oraz pętli jelitowych - czynnościowo? Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Niejednorodny metabolizm FDG w kręgosłupie- do kontroli. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Dyskopatia C5/6  Inne: Pobudzenie metabolicznie w kanale  kręgowym w topografii rdzenia na poziomie Th11 i Th12, SUV max do 3,5- niecharakterystyczne.  Wartości referencyjne: MBPS SUVmax do 3,5 Prawy płat wątroby SUVmax do 5,0.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono pobudzenie metaboliczne w topografii wejścia do kanału pachwinowego oraz pasmowatych zmian bliznowatych w okolicy pachwinowej do przodu od kości łonowej po stronie prawej - w porównaniu do badania z 02.2023 obraz bez istotnych zmian. Opisane węzły chłonne z miernym pobudzeniem metabolicznym do kontroli. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>5</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>19.12.2023</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy. DLBCL - guz jądra lewego. Usunięte jądro lewe (08.2022). Ocena po zakończeniu immunochemio- i radioterapii. Ocena po 3 miesięcach z uwagi na graniczne wartości SUV- wykluczenie wznowy.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 98mg%</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DLBCL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie esowate skrzywienie przegrody nosowej. Ok. 10mm polipowate zgrubienie błony śluzowej w zachyłku zębodołowym prawej zatoki szczękowej. Drobne zgrubienia błony sluzowej w zachyłku zębodołowym lewej zatoki sczękowej. W tkance podskórnej w okolicy mięśnia półkolcowego głowy po stronie lewej na poziomie C2 zmiana o niskim cieniowaniu (3HU) wielkości 12,5x10mm [Im 143] - włókniak? kaszak? - do oceny miejscowej.  Pojedyncze węzły chłonne szyjne,  wielkości do 10mm.   Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne obwodowe zmiany włókniste w płatach dolnych obu płuc. Ok. 7mm zmiana guzkowo-włóknista w segm. 8 płuca lewego. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca prawego. Pojedyncze drobne pęcherze rozedmowe oraz rozsiane obszary o typie mlecznej szyby w płatach dolnych obu płuc, zwłaszcza obustronnie nadprzeponowo - więcej po stronie lewej.  Brzuch i miednica: Pobudzenie metaboliczne w topografii wejścia do kanału pachwinowego prawego oraz pasmowatych zmian włóknistych w okolicy pachwinowej do przodu od kości łonowej po stronie prawej, SUV max do 3,5 - bez typowego ogniskowego gromadzenia FDG- do kontroli. Odcinkowe pobudzenie metaboliczne w topografii pętli jelitowych - czynnościowo? Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Pobudzenie metaboliczne w obrębie struktur prawego stawu biodrowego - zmiany przeciążeniowo-odczynowe? Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowe kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej oraz wielopoziomowo dyskopatie - ciasna na poziomie C5/C6. Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Niewielka dyskopatia na poziomie L4/L5. Os sacrum arcuatum. Kątowe dobrzuszne zagięcie kości ogonowej. Drobne wyspy kostne w kościach miednicy.   Wartości referencyjne: MBPS SUVmax do 3,3 Prawy płat wątroby SUVmax do 4,6.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech aktywnego metabolicznie procesu chłoniakowego. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>4.6</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/SYLWESTER JASNOS.xlsx
+++ b/pacjenci/SYLWESTER JASNOS.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 97mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Węzły chłonne w tkance podskórnej w okolicy mięśnia półkolcowego głowy po stronie lewej na poziomie C2 wielkości 12x11,5mm [Im 140].   Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.  Brzuch i miednica: Pobudzenie metaboliczne w topografii wchodów do kanałów pachwinowych oraz pasmowatych zmian bliznowatych w okolicach pachwinowych do przodu od kości łonowych obustronnie na długości do 26mm, SUV max do 4,7 - w pierwszej kolejności procesy gojenia, do  oceny w łączności z całością obrazu klinicznego, ew. do USG. Odcinkowo wzmożony metabolizm FDG w topografii żołądka oraz pętli jelitowych, SUV max do 4,7 - czynnościowo? do ew. kontroli w endoskopii. Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym.  Inne: Pobudzenie metabolicznie w kanale  kręgowym w topografii rdzenia na poziomie Th11 i Th12, SUV max do 3,7.   Wartości referencyjne: MBPS SUVmax 2,5 Prawy płat wątroby SUVmax do 3,5</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Węzły chłonne w tkance podskórnej w okolicy mięśnia półkolcowego głowy po stronie lewej na poziomie C2 wielkości 12x11,5mm [Im 140].</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w topografii wchodów do kanałów pachwinowych oraz pasmowatych zmian bliznowatych w okolicach pachwinowych do przodu od kości łonowych obustronnie na długości do 26mm, SUV max do 4,7 - w pierwszej kolejności procesy gojenia, do  oceny w łączności z całością obrazu klinicznego, ew. do USG. Odcinkowo wzmożony metabolizm FDG w topografii żołądka oraz pętli jelitowych, SUV max do 4,7 - czynnościowo? do ew. kontroli w endoskopii. Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym.  Inne: Pobudzenie metabolicznie w kanale  kręgowym w topografii rdzenia na poziomie Th11 i Th12, SUV max do 3,7.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono pobudzenie metaboliczne w topografii wchodów do kanałów pachwinowych oraz pasmowatych zmian bliznowatych w okolicach pachwinowych do przodu od kości łonowych obustronnie  - w pierwszej kolejności procesy gojenia,  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>4.7</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 12 min od podania 18F-FDG. Glikemia: 100mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Węzły chłonne w tkance podskórnej w okolicy mięśnia półkolcowego głowy po stronie lewej na poziomie C2 wielkości 12x10mm [Im 140].   Klatka piersiowa i śródpiersie: Pobudzenie metaboliczne we wnęce prawej o wielkości 10x8mm wg PET, SUV max 3,5 [Im 116] - w pierwszej kolejności węzeł chłonny. Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.  Brzuch i miednica: Pobudzenie metaboliczne w topografii wejścia do kanału pachwinowego oraz pasmowatych zmian bliznowatych w okolicy pachwinowej do przodu od kości łonowej po stronie prawej na długości do 13mm, SUV max do 3,7 - w pierwszej kolejności procesy gojenia, do  oceny w łączności z całością obrazu klinicznego, ew. do USG. Odcinkowo wzmożony metabolizm FDG w topografii żołądka oraz pętli jelitowych, SUV max do 5,9 - czynnościowo? do ew. kontroli w endoskopii. Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Dyskopatia C5/6  Inne: Pobudzenie metabolicznie w kanale  kręgowym w topografii rdzenia na poziomie Th11 i Th12, SUV max do 3,7.   Wartości referencyjne: MBPS SUVmax 2,7 Prawy płat wątroby SUVmax do 4,5,</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Węzły chłonne w tkance podskórnej w okolicy mięśnia półkolcowego głowy po stronie lewej na poziomie C2 wielkości 12x10mm [Im 140].</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne we wnęce prawej o wielkości 10x8mm wg PET, SUV max 3,5 [Im 116] - w pierwszej kolejności węzeł chłonny. Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w topografii wejścia do kanału pachwinowego oraz pasmowatych zmian bliznowatych w okolicy pachwinowej do przodu od kości łonowej po stronie prawej na długości do 13mm, SUV max do 3,7 - w pierwszej kolejności procesy gojenia, do  oceny w łączności z całością obrazu klinicznego, ew. do USG. Odcinkowo wzmożony metabolizm FDG w topografii żołądka oraz pętli jelitowych, SUV max do 5,9 - czynnościowo? do ew. kontroli w endoskopii. Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Dyskopatia C5/6  Inne: Pobudzenie metabolicznie w kanale  kręgowym w topografii rdzenia na poziomie Th11 i Th12, SUV max do 3,7.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono pobudzenie metaboliczne we wnęce prawej - w pierwszej kolejności węzeł chłonny - do kontroli. Poza tym uwidoczniono pobudzenie metaboliczne w topografii wejścia do kanału pachwinowego oraz pasmowatych zmian bliznowatych w okolicy pachwinowej do przodu od kości łonowej po stronie prawej (mniejsze niż w badaniu z dnia 04.10.2022) - w pierwszej kolejności procesy gojenia. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>5.9</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 56min od podania 18F-FDG. Glikemia: 102mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Miernie pobudzone metabolicznie węzły chłonne przedziału II obustronnie wielkości do 15mm , SUV max do 3,3 - do kontroli.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. W tkance podskórnej w okolicy mięśnia półkolcowego głowy po stronie lewej na poziomie C2 zmiana o niskim cieniowaniu (3HU) wielkości 12x10mm [Im 140] - kaszak ? do oceny miejscowej.   Klatka piersiowa i śródpiersie: Mierne pobudzenie metaboliczne we wnęce prawej  SUV max 3,6 [Im 120] - do ew. kontroli w badaniu TK z kontrastem dożylnym celem wykluczenia obecności węzła chłonnego.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pasmowate zmiany bliznowato-włókniste w płacie środkowym płuca prawego.  Brzuch i miednica: Pobudzenie metaboliczne w topografii wejścia do kanału pachwinowego prawego oraz pasmowatych zmian bliznowatych w okolicy pachwinowej do przodu od kości łonowej po stronie prawej na długości do 16mm, SUV max do 3,8 - w porównaniu do badania z 02.2023 obraz bez istotnych zmian. Odcinkowo wzmożony metabolizm FDG w topografii żołądka, dwunastnicy oraz pętli jelitowych - czynnościowo? Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Niejednorodny metabolizm FDG w kręgosłupie- do kontroli. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Dyskopatia C5/6  Inne: Pobudzenie metabolicznie w kanale  kręgowym w topografii rdzenia na poziomie Th11 i Th12, SUV max do 3,5- niecharakterystyczne.  Wartości referencyjne: MBPS SUVmax do 3,5 Prawy płat wątroby SUVmax do 5,0.</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Miernie pobudzone metabolicznie węzły chłonne przedziału II obustronnie wielkości do 15mm , SUV max do 3,3 - do kontroli.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. W tkance podskórnej w okolicy mięśnia półkolcowego głowy po stronie lewej na poziomie C2 zmiana o niskim cieniowaniu (3HU) wielkości 12x10mm [Im 140] - kaszak ? do oceny miejscowej.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Mierne pobudzenie metaboliczne we wnęce prawej  SUV max 3,6 [Im 120] - do ew. kontroli w badaniu TK z kontrastem dożylnym celem wykluczenia obecności węzła chłonnego.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pasmowate zmiany bliznowato-włókniste w płacie środkowym płuca prawego.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w topografii wejścia do kanału pachwinowego prawego oraz pasmowatych zmian bliznowatych w okolicy pachwinowej do przodu od kości łonowej po stronie prawej na długości do 16mm, SUV max do 3,8 - w porównaniu do badania z 02.2023 obraz bez istotnych zmian. Odcinkowo wzmożony metabolizm FDG w topografii żołądka, dwunastnicy oraz pętli jelitowych - czynnościowo? Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w kręgosłupie- do kontroli. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Dyskopatia C5/6  Inne: Pobudzenie metabolicznie w kanale  kręgowym w topografii rdzenia na poziomie Th11 i Th12, SUV max do 3,5- niecharakterystyczne.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono pobudzenie metaboliczne w topografii wejścia do kanału pachwinowego oraz pasmowatych zmian bliznowatych w okolicy pachwinowej do przodu od kości łonowej po stronie prawej - w porównaniu do badania z 02.2023 obraz bez istotnych zmian. Opisane węzły chłonne z miernym pobudzeniem metabolicznym do kontroli. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 98mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie esowate skrzywienie przegrody nosowej. Ok. 10mm polipowate zgrubienie błony śluzowej w zachyłku zębodołowym prawej zatoki szczękowej. Drobne zgrubienia błony sluzowej w zachyłku zębodołowym lewej zatoki sczękowej. W tkance podskórnej w okolicy mięśnia półkolcowego głowy po stronie lewej na poziomie C2 zmiana o niskim cieniowaniu (3HU) wielkości 12,5x10mm [Im 143] - włókniak? kaszak? - do oceny miejscowej.  Pojedyncze węzły chłonne szyjne,  wielkości do 10mm.   Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne obwodowe zmiany włókniste w płatach dolnych obu płuc. Ok. 7mm zmiana guzkowo-włóknista w segm. 8 płuca lewego. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca prawego. Pojedyncze drobne pęcherze rozedmowe oraz rozsiane obszary o typie mlecznej szyby w płatach dolnych obu płuc, zwłaszcza obustronnie nadprzeponowo - więcej po stronie lewej.  Brzuch i miednica: Pobudzenie metaboliczne w topografii wejścia do kanału pachwinowego prawego oraz pasmowatych zmian włóknistych w okolicy pachwinowej do przodu od kości łonowej po stronie prawej, SUV max do 3,5 - bez typowego ogniskowego gromadzenia FDG- do kontroli. Odcinkowe pobudzenie metaboliczne w topografii pętli jelitowych - czynnościowo? Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Pobudzenie metaboliczne w obrębie struktur prawego stawu biodrowego - zmiany przeciążeniowo-odczynowe? Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowe kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej oraz wielopoziomowo dyskopatie - ciasna na poziomie C5/C6. Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Niewielka dyskopatia na poziomie L4/L5. Os sacrum arcuatum. Kątowe dobrzuszne zagięcie kości ogonowej. Drobne wyspy kostne w kościach miednicy.   Wartości referencyjne: MBPS SUVmax do 3,3 Prawy płat wątroby SUVmax do 4,6.</t>
+          <t>98</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie esowate skrzywienie przegrody nosowej. Ok. 10mm polipowate zgrubienie błony śluzowej w zachyłku zębodołowym prawej zatoki szczękowej. Drobne zgrubienia błony sluzowej w zachyłku zębodołowym lewej zatoki sczękowej. W tkance podskórnej w okolicy mięśnia półkolcowego głowy po stronie lewej na poziomie C2 zmiana o niskim cieniowaniu (3HU) wielkości 12,5x10mm [Im 143] - włókniak? kaszak? - do oceny miejscowej.  Pojedyncze węzły chłonne szyjne,  wielkości do 10mm.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne obwodowe zmiany włókniste w płatach dolnych obu płuc. Ok. 7mm zmiana guzkowo-włóknista w segm. 8 płuca lewego. Niewielkie zmiany miąższowo-włókniste w segm. 5 płuca prawego. Pojedyncze drobne pęcherze rozedmowe oraz rozsiane obszary o typie mlecznej szyby w płatach dolnych obu płuc, zwłaszcza obustronnie nadprzeponowo - więcej po stronie lewej.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w topografii wejścia do kanału pachwinowego prawego oraz pasmowatych zmian włóknistych w okolicy pachwinowej do przodu od kości łonowej po stronie prawej, SUV max do 3,5 - bez typowego ogniskowego gromadzenia FDG- do kontroli. Odcinkowe pobudzenie metaboliczne w topografii pętli jelitowych - czynnościowo? Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w obrębie struktur prawego stawu biodrowego - zmiany przeciążeniowo-odczynowe? Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowe kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej oraz wielopoziomowo dyskopatie - ciasna na poziomie C5/C6. Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Niewielka dyskopatia na poziomie L4/L5. Os sacrum arcuatum. Kątowe dobrzuszne zagięcie kości ogonowej. Drobne wyspy kostne w kościach miednicy.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech aktywnego metabolicznie procesu chłoniakowego. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>4.6</v>
       </c>
     </row>
